--- a/CHOICES/Ralph Benjamin Libao.xlsx
+++ b/CHOICES/Ralph Benjamin Libao.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tmp\Participants\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FakeDrive\Documents\Scripts\Python\pool2024\CHOICES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B226C2E1-E1BF-40FB-BC94-5676091C544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E055D32F-1519-44BE-A376-C94D5E6EE899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{199FEBA7-5547-4399-8CA2-B58F7145E93D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet20" sheetId="30" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="31" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -758,13 +758,13 @@
     <t>1.19 </t>
   </si>
   <si>
-    <t>Elite Contenders</t>
-  </si>
-  <si>
     <t>X </t>
   </si>
   <si>
     <t> X</t>
+  </si>
+  <si>
+    <t>1. Elite Contenders</t>
   </si>
 </sst>
 </file>
@@ -1341,13 +1341,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA828FE-603E-4896-85FD-867705298E10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFFCC7D-0E81-4100-AC41-1B2E8568EEE6}">
   <dimension ref="A1:K72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="21"/>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="6" t="s">
@@ -1447,7 +1447,9 @@
       <c r="J4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="8"/>
+      <c r="K4" s="8" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -1524,7 +1526,7 @@
       </c>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>31</v>
       </c>
@@ -1547,9 +1549,7 @@
       <c r="J8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>240</v>
-      </c>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
@@ -1662,9 +1662,7 @@
       <c r="J13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
@@ -1689,16 +1687,20 @@
       <c r="J14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="8"/>
+      <c r="C15" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="6" t="s">
         <v>55</v>
@@ -1723,9 +1725,7 @@
       <c r="B16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="C16" s="8"/>
       <c r="D16" s="2"/>
       <c r="E16" s="6" t="s">
         <v>60</v>
@@ -1734,7 +1734,7 @@
         <v>61</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="6" t="s">
@@ -1833,7 +1833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>73</v>
       </c>
@@ -1881,9 +1881,7 @@
       <c r="J22" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
@@ -1893,7 +1891,7 @@
         <v>82</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="6" t="s">
@@ -1902,9 +1900,7 @@
       <c r="F23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="G23" s="8"/>
       <c r="H23" s="2"/>
       <c r="I23" s="6" t="s">
         <v>84</v>
@@ -1929,7 +1925,9 @@
       <c r="F24" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="H24" s="2"/>
       <c r="I24" s="6" t="s">
         <v>88</v>
@@ -1962,9 +1960,11 @@
       <c r="J25" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="26" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>94</v>
       </c>
@@ -2059,9 +2059,7 @@
       <c r="B30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>241</v>
-      </c>
+      <c r="C30" s="8"/>
       <c r="D30" s="2"/>
       <c r="E30" s="6" t="s">
         <v>102</v>
@@ -2095,7 +2093,7 @@
         <v>108</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="6" t="s">
@@ -2129,9 +2127,7 @@
       <c r="J32" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
@@ -2140,7 +2136,9 @@
       <c r="B33" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="8"/>
+      <c r="C33" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="6" t="s">
         <v>117</v>
@@ -2206,7 +2204,9 @@
       <c r="J35" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="K35" s="11"/>
+      <c r="K35" s="11" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="36" spans="1:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
@@ -2286,9 +2286,7 @@
       <c r="F39" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G39" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="G39" s="8"/>
       <c r="H39" s="2"/>
       <c r="I39" s="6" t="s">
         <v>131</v>
@@ -2305,9 +2303,7 @@
       <c r="B40" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>241</v>
-      </c>
+      <c r="C40" s="8"/>
       <c r="D40" s="2"/>
       <c r="E40" s="6" t="s">
         <v>134</v>
@@ -2315,7 +2311,9 @@
       <c r="F40" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="G40" s="8"/>
+      <c r="G40" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="H40" s="2"/>
       <c r="I40" s="6" t="s">
         <v>136</v>
@@ -2373,9 +2371,7 @@
       <c r="J42" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="K42" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
@@ -2400,7 +2396,9 @@
       <c r="J43" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="K43" s="8"/>
+      <c r="K43" s="8" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="44" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
@@ -2409,7 +2407,9 @@
       <c r="B44" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="11"/>
+      <c r="C44" s="11" t="s">
+        <v>239</v>
+      </c>
       <c r="D44" s="2"/>
       <c r="E44" s="9" t="s">
         <v>152</v>
@@ -2497,7 +2497,9 @@
       <c r="B48" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C48" s="8"/>
+      <c r="C48" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="D48" s="2"/>
       <c r="E48" s="6" t="s">
         <v>159</v>
@@ -2515,7 +2517,7 @@
       </c>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>162</v>
       </c>
@@ -2590,16 +2592,14 @@
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>178</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="C52" s="8"/>
       <c r="D52" s="2"/>
       <c r="E52" s="6" t="s">
         <v>179</v>
@@ -2633,7 +2633,7 @@
         <v>8</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="9" t="s">
@@ -2716,7 +2716,9 @@
       <c r="B57" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C57" s="8"/>
+      <c r="C57" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="D57" s="2"/>
       <c r="E57" s="6" t="s">
         <v>190</v>
@@ -2749,7 +2751,9 @@
       <c r="F58" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G58" s="18"/>
+      <c r="G58" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="H58" s="2"/>
       <c r="I58" s="6" t="s">
         <v>195</v>
@@ -2757,9 +2761,11 @@
       <c r="J58" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="K58" s="8"/>
-    </row>
-    <row r="59" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K58" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>197</v>
       </c>
@@ -2782,9 +2788,7 @@
       <c r="J59" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="K59" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
@@ -2818,9 +2822,7 @@
       <c r="B61" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>240</v>
-      </c>
+      <c r="C61" s="8"/>
       <c r="D61" s="2"/>
       <c r="E61" s="6" t="s">
         <v>206</v>
@@ -2828,9 +2830,7 @@
       <c r="F61" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G61" s="8" t="s">
-        <v>241</v>
-      </c>
+      <c r="G61" s="8"/>
       <c r="H61" s="2"/>
       <c r="I61" s="6" t="s">
         <v>207</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="K61" s="8"/>
     </row>
-    <row r="62" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>209</v>
       </c>
@@ -2953,14 +2953,16 @@
       </c>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>220</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C67" s="8"/>
+      <c r="C67" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="D67" s="2"/>
       <c r="E67" s="6" t="s">
         <v>221</v>
@@ -2976,7 +2978,9 @@
       <c r="J67" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="K67" s="8"/>
+      <c r="K67" s="8" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="68" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
@@ -3003,7 +3007,7 @@
       </c>
       <c r="K68" s="8"/>
     </row>
-    <row r="69" spans="1:11" ht="94.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>227</v>
       </c>
@@ -3043,7 +3047,9 @@
       <c r="F70" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="G70" s="8"/>
+      <c r="G70" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="H70" s="2"/>
       <c r="I70" s="6" t="s">
         <v>234</v>
@@ -3060,9 +3066,7 @@
       <c r="B71" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="11" t="s">
-        <v>240</v>
-      </c>
+      <c r="C71" s="11"/>
       <c r="D71" s="2"/>
       <c r="E71" s="9" t="s">
         <v>236</v>
@@ -3070,9 +3074,7 @@
       <c r="F71" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="G71" s="11" t="s">
-        <v>240</v>
-      </c>
+      <c r="G71" s="11"/>
       <c r="H71" s="2"/>
       <c r="I71" s="9" t="s">
         <v>237</v>
@@ -3080,9 +3082,7 @@
       <c r="J71" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="K71" s="11" t="s">
-        <v>240</v>
-      </c>
+      <c r="K71" s="11"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
